--- a/results/by_outcome/full_results_education_observed_Sisters_MI.xlsx
+++ b/results/by_outcome/full_results_education_observed_Sisters_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.579846880475221</v>
+        <v>0.590920429555167</v>
       </c>
       <c r="I2" t="n">
-        <v>0.195069399568557</v>
+        <v>0.247589958219889</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.420358176900945</v>
+        <v>0.409288658377718</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.566699311087391</v>
+        <v>0.589638739984309</v>
       </c>
       <c r="G3" t="n">
-        <v>0.239638189001121</v>
+        <v>0.283390799023655</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.604017668620019</v>
+        <v>0.604096999436549</v>
       </c>
       <c r="D4" t="n">
-        <v>0.396336098359715</v>
+        <v>0.396256960283055</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00035376697973</v>
+        <v>1.0003539597196</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.396195937348151</v>
+        <v>0.396116750876159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.23955344255306</v>
+        <v>0.283290526103614</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0131429199648666</v>
+        <v>-0.00128123608334877</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0241622395527943</v>
+        <v>0.0131719075015598</v>
       </c>
       <c r="N4" t="n">
-        <v>0.226410522588194</v>
+        <v>0.282009290020265</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.396195937348151</v>
+        <v>0.396116750876159</v>
       </c>
       <c r="D2" t="n">
-        <v>0.340431719202329</v>
+        <v>0.335343180263125</v>
       </c>
       <c r="E2" t="n">
-        <v>0.451960155493973</v>
+        <v>0.456890321489192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000000000000000000000000000000000000000000445084316777889</v>
+        <v>0.000000000000000000000000000000000000226522616641709</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.226410522588194</v>
+        <v>0.282009290020265</v>
       </c>
       <c r="D3" t="n">
-        <v>0.170733931342255</v>
+        <v>0.224367599771754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.282087113834132</v>
+        <v>0.339650980268776</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00000000000000303628781463606</v>
+        <v>0.000000000000000000000946620149086027</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.420358176900945</v>
+        <v>0.409288658377718</v>
       </c>
       <c r="D4" t="n">
-        <v>0.361593897065421</v>
+        <v>0.349970776470843</v>
       </c>
       <c r="E4" t="n">
-        <v>0.479122456736469</v>
+        <v>0.468606540284594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00000000000000000000000000000000000000000209310622122353</v>
+        <v>0.0000000000000000000000000000000000000000126028002353621</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.193947654312751</v>
+        <v>0.127279368357453</v>
       </c>
       <c r="D5" t="n">
-        <v>0.156271461415074</v>
+        <v>0.0997599560311966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.231623847210429</v>
+        <v>0.15479878068371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000000000000000000000159396686282414</v>
+        <v>0.000000000000000000262988601138009</v>
       </c>
     </row>
   </sheetData>
